--- a/www/terminologies/ValueSet-JDV-J138-TypeActivite-RASS.xlsx
+++ b/www/terminologies/ValueSet-JDV-J138-TypeActivite-RASS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="117">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>retired</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -337,6 +337,12 @@
   </si>
   <si>
     <t>Information des Tuteurs Familiaux</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Accueil familial</t>
   </si>
   <si>
     <t>60</t>
@@ -619,7 +625,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -975,15 +981,23 @@
         <v>112</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>114</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
